--- a/experiment_results/wu_calibration/rtt_bursts_rps1_att4_WU500000.xlsx
+++ b/experiment_results/wu_calibration/rtt_bursts_rps1_att4_WU500000.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.3</t>
+          <t>00:020.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.2</t>
+          <t>00:029.9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21273</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.2</t>
+          <t>00:039.9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,22 +709,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>43.3</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>59.3</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>20380</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.1</t>
+          <t>00:059.8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64409</t>
+          <t>21611</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.0</t>
+          <t>01:010.3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>73747</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.0</t>
+          <t>01:019.9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>82140</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.0</t>
+          <t>01:030.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>90984</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.9</t>
+          <t>01:040.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>94741</t>
+          <t>50791</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:050.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>99751</t>
+          <t>58350</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.8</t>
+          <t>02:000.2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.18</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>103621</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.1</t>
+          <t>02:010.3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.10</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>107566</t>
+          <t>93150</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.0</t>
+          <t>02:019.7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>113633</t>
+          <t>110701</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:029.7</t>
+          <t>02:030.2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>117913</t>
+          <t>122608</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.7</t>
+          <t>02:039.5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>118728</t>
+          <t>123640</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.3</t>
+          <t>02:049.9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>114030</t>
+          <t>116357</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.8</t>
+          <t>02:055.2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>110584</t>
+          <t>112606</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
